--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2283,8 +2390,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2295,580 +2406,553 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구 아리랑 — 민요채보-2/구 아리랑.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">구 아리랑</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">십</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-―</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">仲
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">개</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">발</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">넘</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">난</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G13" s="14"/>
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="15"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="15"/>
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -620,12 +620,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -797,12 +797,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -938,14 +938,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑|―</t>
+          <t xml:space="preserve">仲|姑|–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無|姑</t>
+          <t xml:space="preserve">–|無|姑</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 姑</t>
         </is>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="2"/>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -1815,14 +1815,14 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑|―</t>
+          <t xml:space="preserve">仲|姑|–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -1958,14 +1958,14 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢|―</t>
+          <t xml:space="preserve">無|潢|–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2255,14 +2255,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑|―</t>
+          <t xml:space="preserve">仲|姑|–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2319,7 +2319,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="8"/>
@@ -2369,7 +2369,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="10"/>
@@ -2388,7 +2388,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10"/>
@@ -2399,7 +2399,7 @@
         <is>
           <t xml:space="preserve">無
 潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="C6" s="8"/>
@@ -2436,7 +2436,7 @@
       <c r="C7" s="9"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
@@ -2556,7 +2556,7 @@
       <c r="G10" s="9"/>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="9"/>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="10"/>
@@ -2645,7 +2645,7 @@
       <c r="E13" s="9"/>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 姑</t>
         </is>
@@ -2665,7 +2665,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C14" s="10"/>
@@ -2673,7 +2673,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E14" s="10"/>
@@ -2688,7 +2688,7 @@
         <is>
           <t xml:space="preserve">仲
 姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="10"/>

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2293,183 +2322,183 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">구 아리랑</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 姑</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
+      <c r="I3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="24"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 無</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="24"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="24"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="24"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 –</t>
         </is>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 姑</t>
         </is>
       </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲
 姑</t>
         </is>
       </c>
-      <c r="I6" s="8"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="23"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">겹쳐 써 불확실</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
@@ -2477,221 +2506,221 @@
 仲</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">겹쳐 써 불확실</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">겹쳐 써 불확실</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="24"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="23"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">겹쳐 써 불확실</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="8"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">겹쳐 써 불확실</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無
 姑</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 –</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="24"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 –</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="24"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="24"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 –</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -2307,20 +2307,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2404,14 +2404,14 @@
       <c r="C5" s="24"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="I5" s="24"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2525,13 +2525,13 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="I8" s="24"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="I9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -2688,7 +2688,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2700,7 +2700,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
         <v>83</v>
       </c>
@@ -2726,7 +2726,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="I5" s="10"/>
     </row>
-    <row r="6" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="8" t="s">
         <v>93</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
         <v>98</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="8" t="s">
         <v>103</v>
       </c>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="I8" s="10"/>
     </row>
-    <row r="9" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
         <v>108</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
         <v>98</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="8" t="s">
         <v>62</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
         <v>47</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
         <v>48</v>
       </c>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="I13" s="9"/>
     </row>
-    <row r="14" customFormat="false" ht="108.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
         <v>127</v>
       </c>

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -301,7 +301,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -310,7 +309,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -349,7 +347,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -359,7 +356,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -367,7 +363,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -378,7 +373,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -388,7 +382,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -410,7 +403,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -420,7 +412,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -433,7 +424,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -443,7 +433,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -451,7 +440,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -468,7 +456,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -478,7 +465,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -491,7 +477,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -501,7 +486,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -509,7 +493,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -527,7 +510,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -536,7 +518,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -571,7 +552,6 @@
   <si>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
         <charset val="1"/>
@@ -580,7 +560,6 @@
     </r>
     <r>
       <rPr>
-        <sz val="24"/>
         <rFont val="궁서체"/>
         <family val="2"/>
       </rPr>
@@ -635,7 +614,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -644,17 +623,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -684,6 +663,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
@@ -773,7 +758,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -815,6 +800,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2677,314 +2694,314 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="18"/>
+      <c r="F5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="18"/>
+      <c r="H5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="17" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="10"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="15" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="18" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="15" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="8" t="s">
+      <c r="E13" s="17"/>
+      <c r="F13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="6" t="s">
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8" t="s">
+      <c r="C14" s="18"/>
+      <c r="D14" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="6" t="s">
+      <c r="E14" s="18"/>
+      <c r="F14" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I14" s="10"/>
+      <c r="I14" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -299,22 +299,8 @@
 姑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">南
+潢</t>
   </si>
   <si>
     <t xml:space="preserve">십
@@ -345,48 +331,12 @@
     <t xml:space="preserve">랑</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無潢
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+    <t xml:space="preserve">–
+–無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無潢
+–</t>
   </si>
   <si>
     <t xml:space="preserve">못</t>
@@ -401,51 +351,15 @@
     <t xml:space="preserve">고</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–南</t>
-    </r>
+    <t xml:space="preserve">無
+–南</t>
   </si>
   <si>
     <t xml:space="preserve">가</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">湳</t>
-    </r>
+    <t xml:space="preserve">–
+–湳</t>
   </si>
   <si>
     <t xml:space="preserve">리</t>
@@ -454,51 +368,15 @@
     <t xml:space="preserve">개</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲姑
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+    <t xml:space="preserve">仲姑
+–</t>
   </si>
   <si>
     <t xml:space="preserve">서</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
+    <t xml:space="preserve">㳞
+–㴌</t>
   </si>
   <si>
     <t xml:space="preserve">로</t>
@@ -508,22 +386,8 @@
 △</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-–</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">潢</t>
-    </r>
+    <t xml:space="preserve">南
+–潢</t>
   </si>
   <si>
     <t xml:space="preserve">발</t>
@@ -550,22 +414,8 @@
 겨</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">南</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">無
+    <t xml:space="preserve">南無
 –南</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">라</t>
@@ -2688,7 +2538,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -2704,8 +2554,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
       <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
@@ -2717,7 +2567,7 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B3" s="14" t="s">
         <v>83</v>
       </c>
@@ -2743,7 +2593,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B4" s="16" t="s">
         <v>58</v>
       </c>
@@ -2769,7 +2619,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B5" s="16" t="s">
         <v>48</v>
       </c>
@@ -2787,7 +2637,7 @@
       </c>
       <c r="I5" s="18"/>
     </row>
-    <row r="6" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B6" s="16" t="s">
         <v>93</v>
       </c>
@@ -2813,7 +2663,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B7" s="16" t="s">
         <v>98</v>
       </c>
@@ -2839,7 +2689,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B8" s="16" t="s">
         <v>103</v>
       </c>
@@ -2863,7 +2713,7 @@
       </c>
       <c r="I8" s="18"/>
     </row>
-    <row r="9" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B9" s="14" t="s">
         <v>108</v>
       </c>
@@ -2889,7 +2739,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B10" s="16" t="s">
         <v>98</v>
       </c>
@@ -2915,7 +2765,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B11" s="16" t="s">
         <v>62</v>
       </c>
@@ -2941,7 +2791,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B12" s="16" t="s">
         <v>47</v>
       </c>
@@ -2967,7 +2817,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B13" s="16" t="s">
         <v>48</v>
       </c>
@@ -2985,7 +2835,7 @@
       </c>
       <c r="I13" s="17"/>
     </row>
-    <row r="14" customFormat="false" ht="82.06" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
       <c r="B14" s="14" t="s">
         <v>127</v>
       </c>
@@ -3009,7 +2859,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/구 아리랑.xlsx
+++ b/sheets/민요/검수/구 아리랑.xlsx
@@ -2544,13 +2544,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="6"/>
   </cols>
   <sheetData>
